--- a/output/pdf_financials_xlsx/GSD.xlsx
+++ b/output/pdf_financials_xlsx/GSD.xlsx
@@ -1537,7 +1537,7 @@
         <v>-4.599607</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.224636</v>
+        <v>-1.224636</v>
       </c>
     </row>
     <row r="24">
@@ -4377,7 +4377,7 @@
         <v>-4.599607</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>1.224636</v>
+        <v>-1.224636</v>
       </c>
     </row>
     <row r="100">
@@ -12827,7 +12827,7 @@
         <v>-4.599607</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>1.224636</v>
+        <v>-1.224636</v>
       </c>
     </row>
     <row r="121">

--- a/output/pdf_financials_xlsx/GSD.xlsx
+++ b/output/pdf_financials_xlsx/GSD.xlsx
@@ -2022,22 +2022,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.498496</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.204883</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.981982</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.24459</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.913017</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.344795</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>2.805191</v>
@@ -2090,22 +2090,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.498496</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.204883</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.981982</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.24459</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.913017</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.344795</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>2.805191</v>
@@ -2498,22 +2498,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.577304</v>
+        <v>0.078808</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.462808</v>
+        <v>0.257925</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.295754</v>
+        <v>0.313772</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.527987</v>
+        <v>0.283397</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.139539</v>
+        <v>0.226522</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.417201</v>
+        <v>0.072406</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>5.142678</v>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">

--- a/output/pdf_financials_xlsx/GSD.xlsx
+++ b/output/pdf_financials_xlsx/GSD.xlsx
@@ -4393,25 +4393,25 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.364467</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.754385</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.7688739999999999</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.765733</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.592787</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.135708</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.370929</v>
       </c>
     </row>
     <row r="101">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">

--- a/output/pdf_financials_xlsx/GSD.xlsx
+++ b/output/pdf_financials_xlsx/GSD.xlsx
@@ -3198,31 +3198,31 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.095239</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.008971</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.552373</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>1.03218</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>1.052772</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>1.23821</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.591894</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.423466</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>10.049394</v>
       </c>
     </row>
     <row r="68">
@@ -3232,31 +3232,31 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.392965</v>
+        <v>0.488204</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.110376</v>
+        <v>0.119347</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>1.19542</v>
+        <v>1.747793</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>1.875644</v>
+        <v>2.907824</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>2.627659</v>
+        <v>3.680431</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>1.809418</v>
+        <v>3.047628</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>1.035177</v>
+        <v>1.627071</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>1.255806</v>
+        <v>1.679272</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>14.025243</v>
+        <v>24.074637</v>
       </c>
     </row>
     <row r="69">
@@ -3476,25 +3476,25 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.469136</v>
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.007257</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.004598</v>
+        <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.686195</v>
+        <v>0.094301</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.021646</v>
+        <v>0</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.044682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
